--- a/artfynd/A 26670-2026 artfynd.xlsx
+++ b/artfynd/A 26670-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134426334</v>
+        <v>134426330</v>
       </c>
       <c r="B2" t="n">
-        <v>58658</v>
+        <v>58131</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>103023</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -757,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,6 +791,125 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>134426334</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gärdsås, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>364936</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6406919</v>
+      </c>
+      <c r="S3" t="n">
+        <v>59</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Töllsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Bo Hultgren</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Bo Hultgren, Erik Vikstrand</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26670-2026 artfynd.xlsx
+++ b/artfynd/A 26670-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134426330</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,8 +920,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134426334</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>